--- a/KatalonData/Bootstrap/Reporting.xlsx
+++ b/KatalonData/Bootstrap/Reporting.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\Bootstrap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7C736E-7B6C-4F65-BC79-C73EF36EA5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F88CBB0-6E37-4532-BCB5-EF5D52C63C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9972" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="APPR" sheetId="1" r:id="rId1"/>
     <sheet name="APER_NewAutopay" sheetId="2" r:id="rId2"/>
     <sheet name="ER_SR" sheetId="3" r:id="rId3"/>
+    <sheet name="PR_SR_CC" sheetId="4" r:id="rId4"/>
+    <sheet name="PR_SR_PC" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="83">
   <si>
     <t>Result</t>
   </si>
@@ -129,115 +130,161 @@
     <t>Thu Jun 04 23:02:06 IST 2026</t>
   </si>
   <si>
-    <t>13</t>
+    <t>10.50</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>CardName</t>
+  </si>
+  <si>
+    <t>TranxCategory</t>
+  </si>
+  <si>
+    <t>CardNumber</t>
+  </si>
+  <si>
+    <t>CSC</t>
+  </si>
+  <si>
+    <t>ExpMM</t>
+  </si>
+  <si>
+    <t>ExpYYYY</t>
+  </si>
+  <si>
+    <t>AL1</t>
+  </si>
+  <si>
+    <t>AL2</t>
+  </si>
+  <si>
+    <t>UDF1</t>
+  </si>
+  <si>
+    <t>UDF2</t>
+  </si>
+  <si>
+    <t>UDF3</t>
+  </si>
+  <si>
+    <t>UDF4</t>
+  </si>
+  <si>
+    <t>UDF5</t>
+  </si>
+  <si>
+    <t>UDF6</t>
+  </si>
+  <si>
+    <t>UDF7</t>
+  </si>
+  <si>
+    <t>UDF8</t>
+  </si>
+  <si>
+    <t>UDF9</t>
+  </si>
+  <si>
+    <t>UDF10</t>
+  </si>
+  <si>
+    <t>411111111111111</t>
+  </si>
+  <si>
+    <t>Florea</t>
+  </si>
+  <si>
+    <t>udf1</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>RETL</t>
+  </si>
+  <si>
+    <t>ZIP</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>839</t>
+  </si>
+  <si>
+    <t>ACHID</t>
+  </si>
+  <si>
+    <t>Mon Sep 14 19:34:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 14 19:49:14 IST 2026</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>10.50</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>744</t>
-  </si>
-  <si>
-    <t>CardName</t>
-  </si>
-  <si>
-    <t>TranxCategory</t>
-  </si>
-  <si>
-    <t>CardNumber</t>
-  </si>
-  <si>
-    <t>CSC</t>
-  </si>
-  <si>
-    <t>ExpMM</t>
-  </si>
-  <si>
-    <t>ExpYYYY</t>
-  </si>
-  <si>
-    <t>AL1</t>
-  </si>
-  <si>
-    <t>AL2</t>
-  </si>
-  <si>
-    <t>UDF1</t>
-  </si>
-  <si>
-    <t>UDF2</t>
-  </si>
-  <si>
-    <t>UDF3</t>
-  </si>
-  <si>
-    <t>UDF4</t>
-  </si>
-  <si>
-    <t>UDF5</t>
-  </si>
-  <si>
-    <t>UDF6</t>
-  </si>
-  <si>
-    <t>UDF7</t>
-  </si>
-  <si>
-    <t>UDF8</t>
-  </si>
-  <si>
-    <t>UDF9</t>
-  </si>
-  <si>
-    <t>UDF10</t>
-  </si>
-  <si>
-    <t>411111111111111</t>
-  </si>
-  <si>
-    <t>Florea</t>
-  </si>
-  <si>
-    <t>udf1</t>
-  </si>
-  <si>
-    <t>Orange</t>
-  </si>
-  <si>
-    <t>RETL</t>
-  </si>
-  <si>
-    <t>ZIP</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Phone</t>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Tue Sep 15 20:55:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 15 21:13:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 19:30:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 20:18:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 21:08:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 21:28:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 21:47:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 21:58:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 22:14:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 22:36:02 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -581,31 +628,31 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="6" width="27.88671875" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" customWidth="1"/>
-    <col min="9" max="9" width="17.77734375" customWidth="1"/>
-    <col min="10" max="10" width="15.44140625" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" customWidth="1"/>
+    <col min="5" max="6" customWidth="true" width="27.88671875"/>
+    <col min="7" max="7" customWidth="true" width="19.0"/>
+    <col min="8" max="8" customWidth="true" width="14.44140625"/>
+    <col min="9" max="9" customWidth="true" width="17.77734375"/>
+    <col min="10" max="10" customWidth="true" width="15.44140625"/>
+    <col min="11" max="11" customWidth="true" width="18.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -625,66 +672,66 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="0">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="0">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="0">
         <v>10</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="0">
         <v>2</v>
       </c>
     </row>
@@ -743,43 +790,43 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>32</v>
+      <c r="B2" t="s" s="0">
+        <v>74</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -806,102 +853,288 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>25</v>
       </c>
       <c r="Q1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="0">
+        <v>123</v>
+      </c>
+      <c r="I2" s="0">
+        <v>12</v>
+      </c>
+      <c r="J2" s="0">
+        <v>2038</v>
+      </c>
+      <c r="P2" s="0">
+        <v>10.01</v>
+      </c>
+      <c r="Q2" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D49DFFE3-C030-4200-BAFF-14BC347FBB0B}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="F2" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2">
-        <v>123</v>
-      </c>
-      <c r="I2">
+        <v>66</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FC7F89-4C97-4617-95F4-AC8FA5987127}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="J2">
-        <v>2038</v>
-      </c>
-      <c r="P2">
-        <v>10.01</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>62</v>
-      </c>
-      <c r="V2" t="s">
-        <v>63</v>
+      <c r="E2" s="0">
+        <v>9</v>
+      </c>
+      <c r="F2" s="0">
+        <v>839</v>
+      </c>
+      <c r="G2" s="0">
+        <v>2.7</v>
+      </c>
+      <c r="H2" s="0">
+        <v>10.5</v>
+      </c>
+      <c r="I2" s="0">
+        <v>1</v>
+      </c>
+      <c r="J2" s="0">
+        <v>1</v>
+      </c>
+      <c r="K2" s="0">
+        <v>4</v>
+      </c>
+      <c r="M2" s="0">
+        <v>2</v>
+      </c>
+      <c r="N2" s="0">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/Bootstrap/Reporting.xlsx
+++ b/KatalonData/Bootstrap/Reporting.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="89">
   <si>
     <t>Result</t>
   </si>
@@ -278,6 +278,24 @@
   </si>
   <si>
     <t>Wed Sep 16 22:36:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 19:28:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 20:12:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 20:28:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 20:42:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 21:04:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 21:24:50 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1028,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
@@ -1104,7 +1122,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>12</v>

--- a/KatalonData/Bootstrap/Reporting.xlsx
+++ b/KatalonData/Bootstrap/Reporting.xlsx
@@ -1,23 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\Bootstrap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F88CBB0-6E37-4532-BCB5-EF5D52C63C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDDE5BC-FE62-4F68-9529-49F683021837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="17280" windowHeight="9972" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="APPR" sheetId="1" r:id="rId1"/>
     <sheet name="APER_NewAutopay" sheetId="2" r:id="rId2"/>
     <sheet name="ER_SR" sheetId="3" r:id="rId3"/>
     <sheet name="PR_SR_CC" sheetId="4" r:id="rId4"/>
-    <sheet name="PR_SR_PC" sheetId="5" r:id="rId5"/>
+    <sheet name="PR_SR_CC_Fail" sheetId="10" r:id="rId5"/>
+    <sheet name="PR_SR_ACH_Fail" sheetId="11" r:id="rId6"/>
+    <sheet name="PR_SR_PC" sheetId="5" r:id="rId7"/>
+    <sheet name="PR_SR_Corp" sheetId="12" r:id="rId8"/>
+    <sheet name="PR_SR_PS" sheetId="13" r:id="rId9"/>
+    <sheet name="SPR_Deferred_CC" sheetId="6" r:id="rId10"/>
+    <sheet name="SPR_Autopay_CC" sheetId="7" r:id="rId11"/>
+    <sheet name="SPR_Deferred_PC" sheetId="8" r:id="rId12"/>
+    <sheet name="SPR_Autopay_ACH" sheetId="9" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="97">
   <si>
     <t>Result</t>
   </si>
@@ -127,9 +135,6 @@
     <t>EmailPhoneID</t>
   </si>
   <si>
-    <t>Thu Jun 04 23:02:06 IST 2026</t>
-  </si>
-  <si>
     <t>10.50</t>
   </si>
   <si>
@@ -238,64 +243,91 @@
     <t>ACHID</t>
   </si>
   <si>
-    <t>Mon Sep 14 19:34:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 14 19:49:14 IST 2026</t>
-  </si>
-  <si>
     <t>2.5</t>
   </si>
   <si>
     <t>38</t>
   </si>
   <si>
-    <t>Tue Sep 15 20:55:34 IST 2026</t>
-  </si>
-  <si>
     <t>Tue Sep 15 21:13:20 IST 2026</t>
   </si>
   <si>
-    <t>Wed Sep 16 19:30:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Sep 16 20:18:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Sep 16 21:08:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Sep 16 21:28:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Sep 16 21:47:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Sep 16 21:58:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Sep 16 22:14:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Sep 16 22:36:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 19:28:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 20:12:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 20:28:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 20:42:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 21:04:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 21:24:50 IST 2026</t>
+    <t>12/31/2025</t>
+  </si>
+  <si>
+    <t>744</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Tue Sep 29 21:50:31 IST 2026</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 20:50:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 19:11:56 IST 2026</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 20:48:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 21:11:53 IST 2026</t>
+  </si>
+  <si>
+    <t>10.11</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 20:14:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 00:46:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:23:39 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Wed Oct 21 21:23:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 21:26:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 21:57:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 22:40:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 22:48:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 21:02:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 21:25:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 21:38:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 21:54:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 22:21:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 22 22:25:32 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -353,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -363,6 +395,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,6 +791,307 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45CC1875-7BF0-42BA-B234-4151711F71DE}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFBB72D0-0860-41BA-B858-39B81B6416AB}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20515725-403B-4344-8B9C-3754B0847C97}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A68AE674-98FB-40CB-A6EE-AC4C15F830D5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C98CD2B-BCF9-4AF8-B5C3-E33763EA4A3E}">
   <dimension ref="A1:N2"/>
@@ -812,39 +1146,39 @@
         <v>11</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -871,70 +1205,70 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="M1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>25</v>
       </c>
       <c r="Q1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
@@ -942,13 +1276,13 @@
         <v>12</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2" s="0">
         <v>123</v>
@@ -963,10 +1297,10 @@
         <v>10.01</v>
       </c>
       <c r="Q2" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="V2" t="s" s="0">
         <v>59</v>
-      </c>
-      <c r="V2" t="s" s="0">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1028,39 +1362,39 @@
         <v>11</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1069,6 +1403,192 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E76D707-02E8-41C3-B64B-39820BA9623E}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C191AB7-5E50-473D-ACCA-3BF688238E89}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="E2" s="0">
+        <v>9</v>
+      </c>
+      <c r="F2" s="0">
+        <v>839</v>
+      </c>
+      <c r="G2" s="0">
+        <v>2.7</v>
+      </c>
+      <c r="H2" s="0">
+        <v>10.02</v>
+      </c>
+      <c r="I2" s="0">
+        <v>1</v>
+      </c>
+      <c r="J2" s="0">
+        <v>1</v>
+      </c>
+      <c r="K2" s="0">
+        <v>4</v>
+      </c>
+      <c r="M2" s="0">
+        <v>2</v>
+      </c>
+      <c r="N2" s="0">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FC7F89-4C97-4617-95F4-AC8FA5987127}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1105,7 +1625,7 @@
         <v>27</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L1" t="s" s="0">
         <v>29</v>
@@ -1122,7 +1642,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>12</v>
@@ -1153,6 +1673,194 @@
       </c>
       <c r="N2" s="0">
         <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF63B942-7065-437D-9EF1-F10B500CF3FB}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AB6CEF-06F8-4D48-B1DE-C9E09F6E39EC}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/Bootstrap/Reporting.xlsx
+++ b/KatalonData/Bootstrap/Reporting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\Bootstrap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDDE5BC-FE62-4F68-9529-49F683021837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8F6611-6FFB-488A-9657-108F39D7F7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="1776" windowWidth="17280" windowHeight="9972" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="9972" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="APPR" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,13 @@
     <sheet name="PR_SR_ACH_Fail" sheetId="11" r:id="rId6"/>
     <sheet name="PR_SR_PC" sheetId="5" r:id="rId7"/>
     <sheet name="PR_SR_Corp" sheetId="12" r:id="rId8"/>
-    <sheet name="PR_SR_PS" sheetId="13" r:id="rId9"/>
-    <sheet name="SPR_Deferred_CC" sheetId="6" r:id="rId10"/>
-    <sheet name="SPR_Autopay_CC" sheetId="7" r:id="rId11"/>
-    <sheet name="SPR_Deferred_PC" sheetId="8" r:id="rId12"/>
-    <sheet name="SPR_Autopay_ACH" sheetId="9" r:id="rId13"/>
+    <sheet name="PR_SR_Corp_Fail" sheetId="14" r:id="rId9"/>
+    <sheet name="PR_SR_PS" sheetId="13" r:id="rId10"/>
+    <sheet name="PR_SR_PS_Fail" sheetId="15" r:id="rId11"/>
+    <sheet name="SPR_Deferred_CC" sheetId="6" r:id="rId12"/>
+    <sheet name="SPR_Autopay_CC" sheetId="7" r:id="rId13"/>
+    <sheet name="SPR_Deferred_PC" sheetId="8" r:id="rId14"/>
+    <sheet name="SPR_Autopay_ACH" sheetId="9" r:id="rId15"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="95">
   <si>
     <t>Result</t>
   </si>
@@ -279,55 +281,49 @@
     <t>Fri Oct 09 20:48:28 IST 2026</t>
   </si>
   <si>
-    <t>Mon Oct 12 21:11:53 IST 2026</t>
-  </si>
-  <si>
     <t>10.11</t>
   </si>
   <si>
     <t>Thu Oct 15 20:14:35 IST 2026</t>
   </si>
   <si>
-    <t>Wed Oct 21 00:46:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Oct 21 16:23:39 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Wed Oct 21 21:23:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Oct 21 21:26:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Oct 21 21:57:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Oct 21 22:40:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Oct 21 22:48:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 22 21:02:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 22 21:25:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 22 21:38:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 22 21:54:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Oct 22 22:21:36 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Oct 22 22:25:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 22:08:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 26 19:24:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 26 20:03:25 IST 2026</t>
+  </si>
+  <si>
+    <t>10.02</t>
+  </si>
+  <si>
+    <t>Mon Oct 26 22:05:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 19:19:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 19:33:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:41:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 21:45:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 21:17:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 21:34:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 21:44:17 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -792,6 +788,194 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AB6CEF-06F8-4D48-B1DE-C9E09F6E39EC}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FAE3C7F-63D6-4130-9E47-C1659FC62247}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45CC1875-7BF0-42BA-B234-4151711F71DE}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -890,7 +1074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFBB72D0-0860-41BA-B858-39B81B6416AB}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -984,7 +1168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20515725-403B-4344-8B9C-3754B0847C97}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1083,7 +1267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A68AE674-98FB-40CB-A6EE-AC4C15F830D5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1456,7 +1640,7 @@
         <v>73</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
@@ -1472,7 +1656,7 @@
         <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>33</v>
@@ -1642,7 +1826,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>12</v>
@@ -1731,10 +1915,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
@@ -1775,7 +1959,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AB6CEF-06F8-4D48-B1DE-C9E09F6E39EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA28B56-4796-426B-AEAE-FE1834C0D198}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1825,10 +2009,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
@@ -1844,20 +2028,20 @@
         <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>33</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>37</v>
